--- a/SDE/student.xlsx
+++ b/SDE/student.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kirat\sem3\SDE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbook/Desktop/SDE_Experiments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8DDFF77-6B14-4539-B2CA-FF63FD621E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD391AF-9A11-8045-A400-56E286567197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8C50B3EA-E587-409F-9180-D8A0A2576946}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14180" xr2:uid="{7974CE32-180C-414A-B107-83CAA3D45E99}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,40 +36,79 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>jas</t>
-  </si>
-  <si>
-    <t>has</t>
-  </si>
-  <si>
-    <t>fas</t>
-  </si>
-  <si>
-    <t>and</t>
-  </si>
-  <si>
-    <t>man</t>
-  </si>
-  <si>
-    <t xml:space="preserve">roll no </t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>marks</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>RollNo</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Marks1</t>
+  </si>
+  <si>
+    <t>Aman</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Riya</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Simran</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Priya</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>G2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -95,8 +134,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,74 +478,146 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A685B079-F25A-45EE-ACCC-7FCFF29F741F}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36ACB690-BDC3-0148-A684-C69944FEC40D}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>101</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D2" s="2">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2">
+        <v>85</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>102</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2">
+        <v>88</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>123</v>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>103</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2">
+        <v>75</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>122</v>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>104</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2">
+        <v>91</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>121</v>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>105</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2">
+        <v>21</v>
+      </c>
+      <c r="E6" s="2">
+        <v>83</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>111</v>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>102</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2">
+        <v>21</v>
+      </c>
+      <c r="E7" s="2">
+        <v>88</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
